--- a/employment_xlsx/PECH_VISITOR_LOG.xlsx
+++ b/employment_xlsx/PECH_VISITOR_LOG.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,34 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -131,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +190,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -236,6 +279,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,8 +598,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -547,69 +621,31 @@
     <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-      <c r="I1" s="1" t="inlineStr"/>
-      <c r="J1" s="1" t="inlineStr"/>
-      <c r="K1" s="1" t="inlineStr"/>
-      <c r="L1" s="1" t="inlineStr"/>
-      <c r="M1" s="1" t="inlineStr"/>
-      <c r="N1" s="1" t="inlineStr"/>
-      <c r="O1" s="1" t="inlineStr"/>
-      <c r="P1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>VISITOR LOG</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -618,283 +654,183 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+      <c r="M7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr"/>
+      <c r="O7" s="1" t="inlineStr"/>
+      <c r="P7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VISITOR LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Daily Visitor Registration  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="1" t="n"/>
-      <c r="O6" s="1" t="n"/>
-      <c r="P6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+      <c r="O12" s="1" t="n"/>
+      <c r="P12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  VISITOR LOG REGISTER</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Visitor Name</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>ID Type</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>ID Number</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Person to See</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Time In</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Time Out</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Badge No.</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Vehicle Reg.</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Items Declared</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n"/>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -914,7 +850,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -934,7 +870,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -954,7 +890,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -974,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -994,7 +930,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -1014,7 +950,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -1034,7 +970,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -1054,7 +990,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -1074,7 +1010,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -1094,7 +1030,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1114,7 +1050,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1134,7 +1070,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1154,7 +1090,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1174,7 +1110,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1194,7 +1130,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1214,7 +1150,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1234,7 +1170,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1254,7 +1190,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1274,7 +1210,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1294,7 +1230,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1314,7 +1250,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1334,7 +1270,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1354,7 +1290,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1374,7 +1310,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
@@ -1394,7 +1330,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
@@ -1414,7 +1350,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
@@ -1434,7 +1370,7 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="11" t="n"/>
@@ -1454,7 +1390,7 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
@@ -1474,7 +1410,7 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="11" t="n"/>
@@ -1494,7 +1430,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
@@ -1514,7 +1450,7 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
@@ -1534,7 +1470,7 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
@@ -1554,7 +1490,7 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="11" t="n"/>
@@ -1574,7 +1510,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
@@ -1594,7 +1530,7 @@
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B51" s="11" t="n"/>
       <c r="C51" s="11" t="n"/>
@@ -1614,7 +1550,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
@@ -1634,7 +1570,7 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="11" t="n"/>
@@ -1654,7 +1590,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
@@ -1674,7 +1610,7 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B55" s="11" t="n"/>
       <c r="C55" s="11" t="n"/>
@@ -1694,7 +1630,7 @@
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
@@ -1714,7 +1650,7 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="11" t="n"/>
@@ -1734,7 +1670,7 @@
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
@@ -1754,7 +1690,7 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="11" t="n"/>
@@ -1774,7 +1710,7 @@
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
@@ -1794,7 +1730,7 @@
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B61" s="11" t="n"/>
       <c r="C61" s="11" t="n"/>
@@ -1814,7 +1750,7 @@
     </row>
     <row r="62">
       <c r="A62" s="10" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
@@ -1834,7 +1770,7 @@
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B63" s="11" t="n"/>
       <c r="C63" s="11" t="n"/>
@@ -1854,7 +1790,7 @@
     </row>
     <row r="64">
       <c r="A64" s="10" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
@@ -1874,7 +1810,7 @@
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B65" s="11" t="n"/>
       <c r="C65" s="11" t="n"/>
@@ -1894,7 +1830,7 @@
     </row>
     <row r="66">
       <c r="A66" s="10" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
@@ -1914,7 +1850,7 @@
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B67" s="11" t="n"/>
       <c r="C67" s="11" t="n"/>
@@ -1934,7 +1870,7 @@
     </row>
     <row r="68">
       <c r="A68" s="10" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
@@ -1954,7 +1890,7 @@
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B69" s="11" t="n"/>
       <c r="C69" s="11" t="n"/>
@@ -1972,69 +1908,218 @@
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="11" t="n"/>
     </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+    </row>
     <row r="71" ht="3" customHeight="1">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="5" t="n"/>
-      <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="n"/>
-      <c r="O71" s="5" t="n"/>
-      <c r="P71" s="5" t="n"/>
+      <c r="A71" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="11" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="11" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="11" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="11" t="n"/>
+      <c r="P71" s="11" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+    </row>
+    <row r="73" ht="3" customHeight="1">
+      <c r="A73" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="11" t="n"/>
+      <c r="F73" s="11" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="11" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="11" t="n"/>
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="11" t="n"/>
+      <c r="P73" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="10" t="n"/>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="11" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="11" t="n"/>
+      <c r="P75" s="11" t="n"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+      <c r="B77" s="5" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="5" t="n"/>
+      <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B72" s="13" t="n"/>
-      <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="13" t="n"/>
-      <c r="H72" s="13" t="n"/>
-      <c r="I72" s="13" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="13" t="n"/>
-      <c r="L72" s="13" t="n"/>
-      <c r="M72" s="13" t="n"/>
-      <c r="N72" s="13" t="n"/>
-      <c r="O72" s="13" t="n"/>
-      <c r="P72" s="13" t="n"/>
-    </row>
-    <row r="73" ht="3" customHeight="1">
-      <c r="A73" s="1" t="n"/>
-      <c r="B73" s="1" t="n"/>
-      <c r="C73" s="1" t="n"/>
-      <c r="D73" s="1" t="n"/>
-      <c r="E73" s="1" t="n"/>
-      <c r="F73" s="1" t="n"/>
-      <c r="G73" s="1" t="n"/>
-      <c r="H73" s="1" t="n"/>
-      <c r="I73" s="1" t="n"/>
-      <c r="J73" s="1" t="n"/>
-      <c r="K73" s="1" t="n"/>
-      <c r="L73" s="1" t="n"/>
-      <c r="M73" s="1" t="n"/>
-      <c r="N73" s="1" t="n"/>
-      <c r="O73" s="1" t="n"/>
-      <c r="P73" s="1" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n"/>
+      <c r="B79" s="1" t="n"/>
+      <c r="C79" s="1" t="n"/>
+      <c r="D79" s="1" t="n"/>
+      <c r="E79" s="1" t="n"/>
+      <c r="F79" s="1" t="n"/>
+      <c r="G79" s="1" t="n"/>
+      <c r="H79" s="1" t="n"/>
+      <c r="I79" s="1" t="n"/>
+      <c r="J79" s="1" t="n"/>
+      <c r="K79" s="1" t="n"/>
+      <c r="L79" s="1" t="n"/>
+      <c r="M79" s="1" t="n"/>
+      <c r="N79" s="1" t="n"/>
+      <c r="O79" s="1" t="n"/>
+      <c r="P79" s="1" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n"/>
+      <c r="B85" s="1" t="n"/>
+      <c r="C85" s="1" t="n"/>
+      <c r="D85" s="1" t="n"/>
+      <c r="E85" s="1" t="n"/>
+      <c r="F85" s="1" t="n"/>
+      <c r="G85" s="1" t="n"/>
+      <c r="H85" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A5:P5"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A8:P8"/>
+    <mergeCell ref="A82:H82"/>
     <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A72:P72"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -2051,5 +2136,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_VISITOR_LOG.xlsx
+++ b/employment_xlsx/PECH_VISITOR_LOG.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visitor Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visitor Log'!$A$9:$P$69</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,34 +61,6 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -159,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,21 +164,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,36 +238,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -621,31 +550,69 @@
     <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
+      <c r="K1" s="1" t="inlineStr"/>
+      <c r="L1" s="1" t="inlineStr"/>
+      <c r="M1" s="1" t="inlineStr"/>
+      <c r="N1" s="1" t="inlineStr"/>
+      <c r="O1" s="1" t="inlineStr"/>
+      <c r="P1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
+          <t>VISITOR LOG</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -654,183 +621,283 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
-      <c r="O7" s="1" t="inlineStr"/>
-      <c r="P7" s="1" t="inlineStr"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>VISITOR LOG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Daily Visitor Registration  |  CONFIDENTIAL</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-      <c r="M12" s="1" t="n"/>
-      <c r="N12" s="1" t="n"/>
-      <c r="O12" s="1" t="n"/>
-      <c r="P12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+      <c r="P6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  VISITOR LOG REGISTER</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Visitor Name</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>ID Type</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>ID Number</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Person to See</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Time In</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Time Out</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Badge No.</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>Vehicle Reg.</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>Items Declared</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
+      <c r="P13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n"/>
+      <c r="P15" s="11" t="n"/>
+    </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -850,7 +917,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -870,7 +937,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -890,7 +957,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -910,7 +977,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -930,7 +997,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -950,7 +1017,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -970,7 +1037,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -990,7 +1057,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -1010,7 +1077,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -1030,7 +1097,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1050,7 +1117,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1070,7 +1137,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1090,7 +1157,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1110,7 +1177,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1130,7 +1197,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1150,7 +1217,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1170,7 +1237,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1190,7 +1257,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1210,7 +1277,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1230,7 +1297,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1250,7 +1317,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1270,7 +1337,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1290,7 +1357,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1310,7 +1377,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
@@ -1330,7 +1397,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
@@ -1350,7 +1417,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
@@ -1370,7 +1437,7 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="11" t="n"/>
@@ -1390,7 +1457,7 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
@@ -1410,7 +1477,7 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="11" t="n"/>
@@ -1430,7 +1497,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
@@ -1450,7 +1517,7 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
@@ -1470,7 +1537,7 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
@@ -1490,7 +1557,7 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="11" t="n"/>
@@ -1510,7 +1577,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
@@ -1530,7 +1597,7 @@
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B51" s="11" t="n"/>
       <c r="C51" s="11" t="n"/>
@@ -1550,7 +1617,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
@@ -1570,7 +1637,7 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="11" t="n"/>
@@ -1590,7 +1657,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
@@ -1610,7 +1677,7 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B55" s="11" t="n"/>
       <c r="C55" s="11" t="n"/>
@@ -1630,7 +1697,7 @@
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
@@ -1650,7 +1717,7 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="11" t="n"/>
@@ -1670,7 +1737,7 @@
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
@@ -1690,7 +1757,7 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="11" t="n"/>
@@ -1710,7 +1777,7 @@
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="10" t="n"/>
@@ -1730,7 +1797,7 @@
     </row>
     <row r="61">
       <c r="A61" s="11" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B61" s="11" t="n"/>
       <c r="C61" s="11" t="n"/>
@@ -1750,7 +1817,7 @@
     </row>
     <row r="62">
       <c r="A62" s="10" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B62" s="10" t="n"/>
       <c r="C62" s="10" t="n"/>
@@ -1770,7 +1837,7 @@
     </row>
     <row r="63">
       <c r="A63" s="11" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B63" s="11" t="n"/>
       <c r="C63" s="11" t="n"/>
@@ -1790,7 +1857,7 @@
     </row>
     <row r="64">
       <c r="A64" s="10" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B64" s="10" t="n"/>
       <c r="C64" s="10" t="n"/>
@@ -1810,7 +1877,7 @@
     </row>
     <row r="65">
       <c r="A65" s="11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B65" s="11" t="n"/>
       <c r="C65" s="11" t="n"/>
@@ -1830,7 +1897,7 @@
     </row>
     <row r="66">
       <c r="A66" s="10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B66" s="10" t="n"/>
       <c r="C66" s="10" t="n"/>
@@ -1850,7 +1917,7 @@
     </row>
     <row r="67">
       <c r="A67" s="11" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B67" s="11" t="n"/>
       <c r="C67" s="11" t="n"/>
@@ -1870,7 +1937,7 @@
     </row>
     <row r="68">
       <c r="A68" s="10" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B68" s="10" t="n"/>
       <c r="C68" s="10" t="n"/>
@@ -1890,7 +1957,7 @@
     </row>
     <row r="69">
       <c r="A69" s="11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B69" s="11" t="n"/>
       <c r="C69" s="11" t="n"/>
@@ -1908,218 +1975,70 @@
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="11" t="n"/>
     </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-    </row>
     <row r="71" ht="3" customHeight="1">
-      <c r="A71" s="11" t="n">
-        <v>56</v>
-      </c>
-      <c r="B71" s="11" t="n"/>
-      <c r="C71" s="11" t="n"/>
-      <c r="D71" s="11" t="n"/>
-      <c r="E71" s="11" t="n"/>
-      <c r="F71" s="11" t="n"/>
-      <c r="G71" s="11" t="n"/>
-      <c r="H71" s="11" t="n"/>
-      <c r="I71" s="11" t="n"/>
-      <c r="J71" s="11" t="n"/>
-      <c r="K71" s="11" t="n"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="11" t="n"/>
-      <c r="O71" s="11" t="n"/>
-      <c r="P71" s="11" t="n"/>
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="5" t="n"/>
+      <c r="J71" s="5" t="n"/>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n"/>
-      <c r="M72" s="10" t="n"/>
-      <c r="N72" s="10" t="n"/>
-      <c r="O72" s="10" t="n"/>
-      <c r="P72" s="10" t="n"/>
-    </row>
-    <row r="73" ht="3" customHeight="1">
-      <c r="A73" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="B73" s="11" t="n"/>
-      <c r="C73" s="11" t="n"/>
-      <c r="D73" s="11" t="n"/>
-      <c r="E73" s="11" t="n"/>
-      <c r="F73" s="11" t="n"/>
-      <c r="G73" s="11" t="n"/>
-      <c r="H73" s="11" t="n"/>
-      <c r="I73" s="11" t="n"/>
-      <c r="J73" s="11" t="n"/>
-      <c r="K73" s="11" t="n"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="11" t="n"/>
-      <c r="O73" s="11" t="n"/>
-      <c r="P73" s="11" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="B75" s="11" t="n"/>
-      <c r="C75" s="11" t="n"/>
-      <c r="D75" s="11" t="n"/>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="11" t="n"/>
-      <c r="G75" s="11" t="n"/>
-      <c r="H75" s="11" t="n"/>
-      <c r="I75" s="11" t="n"/>
-      <c r="J75" s="11" t="n"/>
-      <c r="K75" s="11" t="n"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="11" t="n"/>
-      <c r="O75" s="11" t="n"/>
-      <c r="P75" s="11" t="n"/>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="5" t="n"/>
-      <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="5" t="n"/>
-      <c r="O77" s="5" t="n"/>
-      <c r="P77" s="5" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
+      <c r="A72" s="12" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="n"/>
-      <c r="C79" s="1" t="n"/>
-      <c r="D79" s="1" t="n"/>
-      <c r="E79" s="1" t="n"/>
-      <c r="F79" s="1" t="n"/>
-      <c r="G79" s="1" t="n"/>
-      <c r="H79" s="1" t="n"/>
-      <c r="I79" s="1" t="n"/>
-      <c r="J79" s="1" t="n"/>
-      <c r="K79" s="1" t="n"/>
-      <c r="L79" s="1" t="n"/>
-      <c r="M79" s="1" t="n"/>
-      <c r="N79" s="1" t="n"/>
-      <c r="O79" s="1" t="n"/>
-      <c r="P79" s="1" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n"/>
-      <c r="B85" s="1" t="n"/>
-      <c r="C85" s="1" t="n"/>
-      <c r="D85" s="1" t="n"/>
-      <c r="E85" s="1" t="n"/>
-      <c r="F85" s="1" t="n"/>
-      <c r="G85" s="1" t="n"/>
-      <c r="H85" s="1" t="n"/>
+      <c r="B72" s="13" t="n"/>
+      <c r="C72" s="13" t="n"/>
+      <c r="D72" s="13" t="n"/>
+      <c r="E72" s="13" t="n"/>
+      <c r="F72" s="13" t="n"/>
+      <c r="G72" s="13" t="n"/>
+      <c r="H72" s="13" t="n"/>
+      <c r="I72" s="13" t="n"/>
+      <c r="J72" s="13" t="n"/>
+      <c r="K72" s="13" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
+      <c r="N72" s="13" t="n"/>
+      <c r="O72" s="13" t="n"/>
+      <c r="P72" s="13" t="n"/>
+    </row>
+    <row r="73" ht="3" customHeight="1">
+      <c r="A73" s="1" t="n"/>
+      <c r="B73" s="1" t="n"/>
+      <c r="C73" s="1" t="n"/>
+      <c r="D73" s="1" t="n"/>
+      <c r="E73" s="1" t="n"/>
+      <c r="F73" s="1" t="n"/>
+      <c r="G73" s="1" t="n"/>
+      <c r="H73" s="1" t="n"/>
+      <c r="I73" s="1" t="n"/>
+      <c r="J73" s="1" t="n"/>
+      <c r="K73" s="1" t="n"/>
+      <c r="L73" s="1" t="n"/>
+      <c r="M73" s="1" t="n"/>
+      <c r="N73" s="1" t="n"/>
+      <c r="O73" s="1" t="n"/>
+      <c r="P73" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <autoFilter ref="A9:P69"/>
+  <mergeCells count="5">
     <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A8:P8"/>
-    <mergeCell ref="A82:H82"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A72:P72"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -2135,15 +2054,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>